--- a/artfynd/A 13308-2022 artfynd.xlsx
+++ b/artfynd/A 13308-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13308-2022 artfynd.xlsx
+++ b/artfynd/A 13308-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103995880</v>
+        <v>103995917</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550727.7018058748</v>
+        <v>550667</v>
       </c>
       <c r="R2" t="n">
-        <v>7018530.60410485</v>
+        <v>7018245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Borgvattnet</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103995906</v>
+        <v>103995942</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219880</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550735.7710433987</v>
+        <v>550664</v>
       </c>
       <c r="R3" t="n">
-        <v>7018447.494094073</v>
+        <v>7018349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +851,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Borgvattnet</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103995942</v>
+        <v>103995964</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550664.3378868987</v>
+        <v>550708</v>
       </c>
       <c r="R4" t="n">
-        <v>7018348.730137479</v>
+        <v>7018544</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ragunda</t>
+          <t>Borgvattnet</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,37 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103995973</v>
+        <v>103995933</v>
       </c>
       <c r="B5" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550737.8316167539</v>
+        <v>550618</v>
       </c>
       <c r="R5" t="n">
-        <v>7018459.674884255</v>
+        <v>7018365</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,6 +1114,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Brandljud vårtbjörk över 200år</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1159,15 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995850</v>
+        <v>103995835</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550691.3422594393</v>
+        <v>550700</v>
       </c>
       <c r="R6" t="n">
-        <v>7018665.005582302</v>
+        <v>7018537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,37 +1260,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995852</v>
+        <v>103995839</v>
       </c>
       <c r="B7" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550674.8324989607</v>
+        <v>550730</v>
       </c>
       <c r="R7" t="n">
-        <v>7018597.708590019</v>
+        <v>7018511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103995964</v>
+        <v>103995880</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550707.6631881632</v>
+        <v>550728</v>
       </c>
       <c r="R8" t="n">
-        <v>7018544.235734277</v>
+        <v>7018530</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,37 +1492,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103995889</v>
+        <v>103995881</v>
       </c>
       <c r="B9" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221343</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1562,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550811.3202348654</v>
+        <v>550672</v>
       </c>
       <c r="R9" t="n">
-        <v>7018570.617594196</v>
+        <v>7018256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1552,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Borgvattnet</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1597,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,15 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103995838</v>
+        <v>103995887</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,21 +1619,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550664.1607247711</v>
+        <v>550672</v>
       </c>
       <c r="R10" t="n">
-        <v>7018359.976092187</v>
+        <v>7018196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1668,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Borgvattnet</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1718,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,37 +1724,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103995903</v>
+        <v>103995824</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1804,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550673.4414399687</v>
+        <v>550675</v>
       </c>
       <c r="R11" t="n">
-        <v>7018257.082327377</v>
+        <v>7018603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1784,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Ragunda</t>
+          <t>Borgvattnet</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1839,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,15 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103995824</v>
+        <v>103995868</v>
       </c>
       <c r="B12" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550674.7545298747</v>
+        <v>550749</v>
       </c>
       <c r="R12" t="n">
-        <v>7018602.65643294</v>
+        <v>7018377</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1970,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,37 +1956,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103995881</v>
+        <v>103995914</v>
       </c>
       <c r="B13" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550672.111309706</v>
+        <v>550623</v>
       </c>
       <c r="R13" t="n">
-        <v>7018255.711479989</v>
+        <v>7018358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2016,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Ragunda</t>
+          <t>Borgvattnet</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2081,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,15 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103995972</v>
+        <v>103995930</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2167,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550669.1817344023</v>
+        <v>550669</v>
       </c>
       <c r="R14" t="n">
-        <v>7018270.064128537</v>
+        <v>7018229</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,37 +2188,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103995917</v>
+        <v>103995972</v>
       </c>
       <c r="B15" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2288,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550666.4253527527</v>
+        <v>550669</v>
       </c>
       <c r="R15" t="n">
-        <v>7018244.822756819</v>
+        <v>7018270</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2333,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,15 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103995914</v>
+        <v>103995973</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,21 +2315,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2409,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550623.1839455394</v>
+        <v>550738</v>
       </c>
       <c r="R16" t="n">
-        <v>7018358.430931062</v>
+        <v>7018460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2444,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2454,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,37 +2420,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103995867</v>
+        <v>103995903</v>
       </c>
       <c r="B17" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2530,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550742.9447595592</v>
+        <v>550673</v>
       </c>
       <c r="R17" t="n">
-        <v>7018592.483805805</v>
+        <v>7018257</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,7 +2480,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Borgvattnet</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2565,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2575,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,11 +2511,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -2616,37 +2536,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103995933</v>
+        <v>103995838</v>
       </c>
       <c r="B18" t="n">
-        <v>73685</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550618.1227941879</v>
+        <v>550664</v>
       </c>
       <c r="R18" t="n">
-        <v>7018365.10049767</v>
+        <v>7018360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2701,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,11 +2627,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Brandljud vårtbjörk över 200år</t>
-        </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -2742,37 +2652,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103995839</v>
+        <v>103995867</v>
       </c>
       <c r="B19" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2782,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550730.2732464968</v>
+        <v>550743</v>
       </c>
       <c r="R19" t="n">
-        <v>7018510.397954192</v>
+        <v>7018593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2817,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2827,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,6 +2743,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -2863,37 +2773,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103995835</v>
+        <v>103995852</v>
       </c>
       <c r="B20" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>219880</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2903,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550699.6619276452</v>
+        <v>550675</v>
       </c>
       <c r="R20" t="n">
-        <v>7018537.360719598</v>
+        <v>7018598</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2938,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2948,7 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,6 +2882,238 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103995906</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Uggleborgsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>550736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7018448</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>103995889</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Uggleborgsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7018570</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 13308-2022 artfynd.xlsx
+++ b/artfynd/A 13308-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995942</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995964</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995933</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995835</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995839</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995881</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995887</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995824</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995868</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2069,6 +2129,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995914</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2185,6 +2250,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995930</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2301,6 +2371,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995972</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2417,6 +2492,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995973</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2533,6 +2613,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995903</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,6 +2734,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995838</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2770,6 +2860,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995867</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2886,6 +2981,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995852</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3002,6 +3102,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995906</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3118,8 +3223,36 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>